--- a/NFL_Odds/Data/WestCoast_ATS_Analysis.xlsx
+++ b/NFL_Odds/Data/WestCoast_ATS_Analysis.xlsx
@@ -12,15 +12,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
   <si>
+    <t xml:space="preserve">Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opponent</t>
+  </si>
+  <si>
     <t xml:space="preserve">Matchup</t>
   </si>
   <si>
-    <t xml:space="preserve">Score</t>
+    <t xml:space="preserve">Team Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opponent Score</t>
   </si>
   <si>
     <t xml:space="preserve">Spread</t>
@@ -29,610 +38,397 @@
     <t xml:space="preserve">Result Indicator</t>
   </si>
   <si>
+    <t xml:space="preserve">SF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR</t>
+  </si>
+  <si>
     <t xml:space="preserve">SF @ CAR</t>
   </si>
   <si>
-    <t xml:space="preserve">27-46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-12.0</t>
+    <t xml:space="preserve">+12.0</t>
   </si>
   <si>
     <t xml:space="preserve">Not Covered</t>
   </si>
   <si>
+    <t xml:space="preserve">LV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAL</t>
+  </si>
+  <si>
     <t xml:space="preserve">OAK @ BAL</t>
   </si>
   <si>
-    <t xml:space="preserve">28-27</t>
+    <t xml:space="preserve">+3.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEA @ NYJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF @ BUF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+7.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OAK @ JAX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OAK @ TB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF @ MIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+7.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Push</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF @ IND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC @ NYG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+3.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF @ WAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OAK @ BUF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC @ NE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF @ PHI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+13.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC @ JAX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+5.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC @ NYJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC @ BUF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OAK @ MIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC @ CLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEA @ DET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEA @ CAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF @ TB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OAK @ CIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF @ CIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC @ DET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEA @ PIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+4.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OAK @ IND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+5.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC @ MIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-15.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEA @ CLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-10.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEA @ ATL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OAK @ NYJ</t>
   </si>
   <si>
     <t xml:space="preserve">-3.5</t>
   </si>
   <si>
-    <t xml:space="preserve">SEA @ NYJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF @ BUF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16-45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OAK @ JAX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33-16</t>
+    <t xml:space="preserve">SEA @ PHI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF @ BAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LV @ CAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF @ NYJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LV @ NE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF @ NYG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEA @ MIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC @ TB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LV @ CLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEA @ BUF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LV @ ATL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+4.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LV @ NYJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEA @ WAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF @ DET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-9.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEA @ IND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC @ WAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LV @ PIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC @ BAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LV @ NYG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF @ JAX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC @ CIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LV @ IND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+8.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF @ ATL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC @ ATL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LV @ JAX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF @ PIT</t>
   </si>
   <si>
     <t xml:space="preserve">-1.5</t>
   </si>
   <si>
-    <t xml:space="preserve">OAK @ TB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF @ MIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF @ IND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAC @ NYG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF @ WAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OAK @ BUF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14-34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAC @ NE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF @ PHI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10-33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-13.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAC @ JAX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17-20</t>
+    <t xml:space="preserve">LV @ BUF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEA @ CIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF @ CLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEA @ BAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LV @ MIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+14.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-14.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LV @ BAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+9.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC @ CAR</t>
   </si>
   <si>
     <t xml:space="preserve">-5.0</t>
   </si>
   <si>
-    <t xml:space="preserve">LAC @ NYJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14-7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAC @ BUF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OAK @ MIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAC @ CLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEA @ DET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17-34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEA @ CAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Push</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF @ TB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OAK @ CIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF @ CIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAC @ DET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEA @ PIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OAK @ IND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31-24</t>
+    <t xml:space="preserve">SEA @ NE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC @ PIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LV @ CIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+8.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LV @ TB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LV @ WAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEA @ JAX</t>
   </si>
   <si>
     <t xml:space="preserve">-5.5</t>
   </si>
   <si>
-    <t xml:space="preserve">LAC @ MIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+15.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEA @ CLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9-0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEA @ ATL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OAK @ NYJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEA @ PHI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17-9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF @ BAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LV @ CAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+3.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF @ NYJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+7.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LV @ NE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF @ NYG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36-9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEA @ MIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+4.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAC @ TB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31-38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LV @ CLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEA @ BUF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34-44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LV @ ATL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6-43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LV @ NYJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEA @ WAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF @ DET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41-33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+9.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEA @ IND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAC @ WAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LV @ PIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAC @ BAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6-34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LV @ NYG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF @ JAX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+6.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAC @ CIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LV @ IND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48-45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF @ ATL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAC @ ATL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+2.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LV @ JAX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF @ PIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30-7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LV @ BUF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10-38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEA @ CIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF @ CLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEA @ BAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LV @ MIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-14.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6-0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+14.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LV @ BAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-9.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAC @ CAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+5.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEA @ NE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAC @ PIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LV @ CIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+2.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19-34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LV @ TB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40-7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LV @ WAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6-40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEA @ JAX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6-35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26-8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+5.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37-9</t>
-  </si>
-  <si>
     <t xml:space="preserve">LV @ PHI</t>
   </si>
   <si>
-    <t xml:space="preserve">0-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-12.5</t>
+    <t xml:space="preserve">+12.5</t>
   </si>
 </sst>
 </file>
@@ -983,22 +779,40 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
         <v>42631</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -1006,16 +820,25 @@
         <v>42645</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
+        <v>15</v>
+      </c>
+      <c r="E3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F3" t="n">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -1023,16 +846,25 @@
         <v>42645</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="E4" t="n">
+        <v>27</v>
+      </c>
+      <c r="F4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -1040,16 +872,25 @@
         <v>42659</v>
       </c>
       <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="n">
         <v>16</v>
       </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
+      <c r="F5" t="n">
+        <v>45</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -1057,16 +898,25 @@
         <v>42666</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
+        <v>26</v>
+      </c>
+      <c r="E6" t="n">
+        <v>33</v>
+      </c>
+      <c r="F6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -1074,16 +924,25 @@
         <v>42673</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" t="n">
+        <v>30</v>
+      </c>
+      <c r="F7" t="n">
         <v>24</v>
       </c>
-      <c r="E7" t="s">
-        <v>15</v>
+      <c r="G7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -1091,16 +950,25 @@
         <v>42701</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
+        <v>32</v>
+      </c>
+      <c r="E8" t="n">
+        <v>24</v>
+      </c>
+      <c r="F8" t="n">
+        <v>31</v>
+      </c>
+      <c r="G8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="9">
@@ -1108,16 +976,25 @@
         <v>43016</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
+        <v>36</v>
+      </c>
+      <c r="E9" t="n">
+        <v>23</v>
+      </c>
+      <c r="F9" t="n">
+        <v>26</v>
+      </c>
+      <c r="G9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -1125,16 +1002,25 @@
         <v>43016</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>15</v>
+        <v>39</v>
+      </c>
+      <c r="E10" t="n">
+        <v>27</v>
+      </c>
+      <c r="F10" t="n">
+        <v>22</v>
+      </c>
+      <c r="G10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -1142,16 +1028,25 @@
         <v>43023</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
+        <v>42</v>
+      </c>
+      <c r="E11" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" t="n">
+        <v>26</v>
+      </c>
+      <c r="G11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -1159,16 +1054,25 @@
         <v>43037</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
+        <v>43</v>
+      </c>
+      <c r="E12" t="n">
+        <v>14</v>
+      </c>
+      <c r="F12" t="n">
+        <v>34</v>
+      </c>
+      <c r="G12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -1176,16 +1080,25 @@
         <v>43037</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
+        <v>46</v>
+      </c>
+      <c r="E13" t="n">
+        <v>13</v>
+      </c>
+      <c r="F13" t="n">
+        <v>21</v>
+      </c>
+      <c r="G13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -1193,16 +1106,25 @@
         <v>43037</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
+        <v>49</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>33</v>
+      </c>
+      <c r="G14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -1210,16 +1132,25 @@
         <v>43051</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
+        <v>51</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17</v>
+      </c>
+      <c r="F15" t="n">
+        <v>20</v>
+      </c>
+      <c r="G15" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -1227,16 +1158,25 @@
         <v>43093</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" t="s">
-        <v>15</v>
+        <v>53</v>
+      </c>
+      <c r="E16" t="n">
+        <v>14</v>
+      </c>
+      <c r="F16" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -1244,16 +1184,25 @@
         <v>43359</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" t="s">
-        <v>15</v>
+        <v>55</v>
+      </c>
+      <c r="E17" t="n">
+        <v>31</v>
+      </c>
+      <c r="F17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G17" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1261,16 +1210,25 @@
         <v>43366</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
+        <v>56</v>
+      </c>
+      <c r="E18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F18" t="n">
+        <v>28</v>
+      </c>
+      <c r="G18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -1278,16 +1236,25 @@
         <v>43387</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" t="s">
-        <v>15</v>
+        <v>58</v>
+      </c>
+      <c r="E19" t="n">
+        <v>38</v>
+      </c>
+      <c r="F19" t="n">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -1295,16 +1262,25 @@
         <v>43401</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" t="s">
-        <v>15</v>
+        <v>60</v>
+      </c>
+      <c r="E20" t="n">
+        <v>28</v>
+      </c>
+      <c r="F20" t="n">
+        <v>14</v>
+      </c>
+      <c r="G20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H20" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1312,16 +1288,25 @@
         <v>43429</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>43</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
+        <v>15</v>
+      </c>
+      <c r="E21" t="n">
+        <v>17</v>
+      </c>
+      <c r="F21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G21" t="s">
+        <v>50</v>
+      </c>
+      <c r="H21" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -1329,16 +1314,25 @@
         <v>43429</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" t="s">
         <v>61</v>
+      </c>
+      <c r="E22" t="n">
+        <v>30</v>
+      </c>
+      <c r="F22" t="n">
+        <v>27</v>
+      </c>
+      <c r="G22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H22" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -1346,16 +1340,25 @@
         <v>43429</v>
       </c>
       <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" t="s">
         <v>62</v>
       </c>
-      <c r="C23" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
+      <c r="E23" t="n">
+        <v>9</v>
+      </c>
+      <c r="F23" t="n">
+        <v>27</v>
+      </c>
+      <c r="G23" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -1363,16 +1366,25 @@
         <v>43450</v>
       </c>
       <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" t="s">
         <v>64</v>
       </c>
-      <c r="C24" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
+      <c r="E24" t="n">
+        <v>16</v>
+      </c>
+      <c r="F24" t="n">
+        <v>30</v>
+      </c>
+      <c r="G24" t="s">
+        <v>40</v>
+      </c>
+      <c r="H24" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="25">
@@ -1380,16 +1392,25 @@
         <v>43723</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" t="s">
-        <v>15</v>
+        <v>65</v>
+      </c>
+      <c r="E25" t="n">
+        <v>41</v>
+      </c>
+      <c r="F25" t="n">
+        <v>17</v>
+      </c>
+      <c r="G25" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="26">
@@ -1397,16 +1418,25 @@
         <v>43723</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
+        <v>66</v>
+      </c>
+      <c r="E26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" t="n">
+        <v>13</v>
+      </c>
+      <c r="G26" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="27">
@@ -1414,16 +1444,25 @@
         <v>43723</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
-        <v>72</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
+        <v>68</v>
+      </c>
+      <c r="E27" t="n">
+        <v>28</v>
+      </c>
+      <c r="F27" t="n">
+        <v>26</v>
+      </c>
+      <c r="G27" t="s">
+        <v>69</v>
+      </c>
+      <c r="H27" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="28">
@@ -1431,16 +1470,25 @@
         <v>43737</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="D28" t="s">
-        <v>75</v>
-      </c>
-      <c r="E28" t="s">
-        <v>15</v>
+        <v>70</v>
+      </c>
+      <c r="E28" t="n">
+        <v>31</v>
+      </c>
+      <c r="F28" t="n">
+        <v>24</v>
+      </c>
+      <c r="G28" t="s">
+        <v>71</v>
+      </c>
+      <c r="H28" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="29">
@@ -1448,16 +1496,25 @@
         <v>43737</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>78</v>
-      </c>
-      <c r="E29" t="s">
-        <v>15</v>
+        <v>72</v>
+      </c>
+      <c r="E29" t="n">
+        <v>30</v>
+      </c>
+      <c r="F29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G29" t="s">
+        <v>73</v>
+      </c>
+      <c r="H29" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="30">
@@ -1465,16 +1522,25 @@
         <v>43751</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="D30" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" t="s">
-        <v>15</v>
+        <v>74</v>
+      </c>
+      <c r="E30" t="n">
+        <v>32</v>
+      </c>
+      <c r="F30" t="n">
+        <v>28</v>
+      </c>
+      <c r="G30" t="s">
+        <v>30</v>
+      </c>
+      <c r="H30" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="31">
@@ -1482,16 +1548,25 @@
         <v>43758</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="D31" t="s">
-        <v>82</v>
-      </c>
-      <c r="E31" t="s">
-        <v>15</v>
+        <v>42</v>
+      </c>
+      <c r="E31" t="n">
+        <v>9</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="s">
+        <v>75</v>
+      </c>
+      <c r="H31" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="32">
@@ -1499,16 +1574,25 @@
         <v>43765</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D32" t="s">
-        <v>49</v>
-      </c>
-      <c r="E32" t="s">
-        <v>15</v>
+        <v>77</v>
+      </c>
+      <c r="E32" t="n">
+        <v>27</v>
+      </c>
+      <c r="F32" t="n">
+        <v>20</v>
+      </c>
+      <c r="G32" t="s">
+        <v>54</v>
+      </c>
+      <c r="H32" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="33">
@@ -1516,16 +1600,25 @@
         <v>43793</v>
       </c>
       <c r="B33" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>87</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
+        <v>78</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>34</v>
+      </c>
+      <c r="G33" t="s">
+        <v>79</v>
+      </c>
+      <c r="H33" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="34">
@@ -1533,16 +1626,25 @@
         <v>43793</v>
       </c>
       <c r="B34" t="s">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="C34" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="D34" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34" t="s">
-        <v>15</v>
+        <v>80</v>
+      </c>
+      <c r="E34" t="n">
+        <v>17</v>
+      </c>
+      <c r="F34" t="n">
+        <v>9</v>
+      </c>
+      <c r="G34" t="s">
+        <v>21</v>
+      </c>
+      <c r="H34" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="35">
@@ -1550,16 +1652,25 @@
         <v>43800</v>
       </c>
       <c r="B35" t="s">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>75</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
+        <v>81</v>
+      </c>
+      <c r="E35" t="n">
+        <v>17</v>
+      </c>
+      <c r="F35" t="n">
+        <v>20</v>
+      </c>
+      <c r="G35" t="s">
+        <v>71</v>
+      </c>
+      <c r="H35" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="36">
@@ -1567,16 +1678,25 @@
         <v>43814</v>
       </c>
       <c r="B36" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="C36" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D36" t="s">
-        <v>91</v>
-      </c>
-      <c r="E36" t="s">
-        <v>15</v>
+        <v>61</v>
+      </c>
+      <c r="E36" t="n">
+        <v>30</v>
+      </c>
+      <c r="F36" t="n">
+        <v>24</v>
+      </c>
+      <c r="G36" t="s">
+        <v>82</v>
+      </c>
+      <c r="H36" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="37">
@@ -1584,16 +1704,25 @@
         <v>44087</v>
       </c>
       <c r="B37" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="D37" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" t="s">
-        <v>15</v>
+        <v>77</v>
+      </c>
+      <c r="E37" t="n">
+        <v>38</v>
+      </c>
+      <c r="F37" t="n">
+        <v>25</v>
+      </c>
+      <c r="G37" t="s">
+        <v>30</v>
+      </c>
+      <c r="H37" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="38">
@@ -1601,16 +1730,25 @@
         <v>44087</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="D38" t="s">
-        <v>95</v>
-      </c>
-      <c r="E38" t="s">
-        <v>15</v>
+        <v>83</v>
+      </c>
+      <c r="E38" t="n">
+        <v>34</v>
+      </c>
+      <c r="F38" t="n">
+        <v>30</v>
+      </c>
+      <c r="G38" t="s">
+        <v>84</v>
+      </c>
+      <c r="H38" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="39">
@@ -1618,16 +1756,25 @@
         <v>44094</v>
       </c>
       <c r="B39" t="s">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="D39" t="s">
-        <v>98</v>
-      </c>
-      <c r="E39" t="s">
-        <v>15</v>
+        <v>85</v>
+      </c>
+      <c r="E39" t="n">
+        <v>31</v>
+      </c>
+      <c r="F39" t="n">
+        <v>13</v>
+      </c>
+      <c r="G39" t="s">
+        <v>86</v>
+      </c>
+      <c r="H39" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="40">
@@ -1635,16 +1782,25 @@
         <v>44101</v>
       </c>
       <c r="B40" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="D40" t="s">
-        <v>27</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
+        <v>87</v>
+      </c>
+      <c r="E40" t="n">
+        <v>20</v>
+      </c>
+      <c r="F40" t="n">
+        <v>36</v>
+      </c>
+      <c r="G40" t="s">
+        <v>33</v>
+      </c>
+      <c r="H40" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="41">
@@ -1652,16 +1808,25 @@
         <v>44101</v>
       </c>
       <c r="B41" t="s">
-        <v>101</v>
+        <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="D41" t="s">
-        <v>95</v>
-      </c>
-      <c r="E41" t="s">
-        <v>15</v>
+        <v>88</v>
+      </c>
+      <c r="E41" t="n">
+        <v>36</v>
+      </c>
+      <c r="F41" t="n">
+        <v>9</v>
+      </c>
+      <c r="G41" t="s">
+        <v>84</v>
+      </c>
+      <c r="H41" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="42">
@@ -1669,16 +1834,25 @@
         <v>44108</v>
       </c>
       <c r="B42" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>104</v>
+        <v>31</v>
       </c>
       <c r="D42" t="s">
-        <v>105</v>
-      </c>
-      <c r="E42" t="s">
-        <v>15</v>
+        <v>89</v>
+      </c>
+      <c r="E42" t="n">
+        <v>31</v>
+      </c>
+      <c r="F42" t="n">
+        <v>23</v>
+      </c>
+      <c r="G42" t="s">
+        <v>90</v>
+      </c>
+      <c r="H42" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="43">
@@ -1686,16 +1860,25 @@
         <v>44108</v>
       </c>
       <c r="B43" t="s">
-        <v>106</v>
+        <v>37</v>
       </c>
       <c r="C43" t="s">
-        <v>107</v>
+        <v>28</v>
       </c>
       <c r="D43" t="s">
-        <v>18</v>
-      </c>
-      <c r="E43" t="s">
-        <v>8</v>
+        <v>91</v>
+      </c>
+      <c r="E43" t="n">
+        <v>31</v>
+      </c>
+      <c r="F43" t="n">
+        <v>38</v>
+      </c>
+      <c r="G43" t="s">
+        <v>24</v>
+      </c>
+      <c r="H43" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="44">
@@ -1703,16 +1886,25 @@
         <v>44136</v>
       </c>
       <c r="B44" t="s">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="D44" t="s">
-        <v>24</v>
-      </c>
-      <c r="E44" t="s">
-        <v>15</v>
+        <v>92</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16</v>
+      </c>
+      <c r="F44" t="n">
+        <v>6</v>
+      </c>
+      <c r="G44" t="s">
+        <v>30</v>
+      </c>
+      <c r="H44" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="45">
@@ -1720,16 +1912,25 @@
         <v>44143</v>
       </c>
       <c r="B45" t="s">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="C45" t="s">
-        <v>111</v>
+        <v>22</v>
       </c>
       <c r="D45" t="s">
-        <v>95</v>
-      </c>
-      <c r="E45" t="s">
-        <v>8</v>
+        <v>93</v>
+      </c>
+      <c r="E45" t="n">
+        <v>34</v>
+      </c>
+      <c r="F45" t="n">
+        <v>44</v>
+      </c>
+      <c r="G45" t="s">
+        <v>84</v>
+      </c>
+      <c r="H45" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="46">
@@ -1737,16 +1938,25 @@
         <v>44164</v>
       </c>
       <c r="B46" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="D46" t="s">
-        <v>87</v>
-      </c>
-      <c r="E46" t="s">
-        <v>8</v>
+        <v>94</v>
+      </c>
+      <c r="E46" t="n">
+        <v>6</v>
+      </c>
+      <c r="F46" t="n">
+        <v>43</v>
+      </c>
+      <c r="G46" t="s">
+        <v>79</v>
+      </c>
+      <c r="H46" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="47">
@@ -1754,16 +1964,25 @@
         <v>44164</v>
       </c>
       <c r="B47" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C47" t="s">
-        <v>114</v>
+        <v>22</v>
       </c>
       <c r="D47" t="s">
-        <v>115</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
+        <v>55</v>
+      </c>
+      <c r="E47" t="n">
+        <v>17</v>
+      </c>
+      <c r="F47" t="n">
+        <v>27</v>
+      </c>
+      <c r="G47" t="s">
+        <v>95</v>
+      </c>
+      <c r="H47" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="48">
@@ -1771,16 +1990,25 @@
         <v>44171</v>
       </c>
       <c r="B48" t="s">
-        <v>116</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="D48" t="s">
-        <v>49</v>
-      </c>
-      <c r="E48" t="s">
-        <v>15</v>
+        <v>96</v>
+      </c>
+      <c r="E48" t="n">
+        <v>31</v>
+      </c>
+      <c r="F48" t="n">
+        <v>28</v>
+      </c>
+      <c r="G48" t="s">
+        <v>54</v>
+      </c>
+      <c r="H48" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="49">
@@ -1788,16 +2016,25 @@
         <v>44185</v>
       </c>
       <c r="B49" t="s">
-        <v>118</v>
+        <v>18</v>
       </c>
       <c r="C49" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="D49" t="s">
-        <v>91</v>
-      </c>
-      <c r="E49" t="s">
+        <v>97</v>
+      </c>
+      <c r="E49" t="n">
+        <v>20</v>
+      </c>
+      <c r="F49" t="n">
         <v>15</v>
+      </c>
+      <c r="G49" t="s">
+        <v>82</v>
+      </c>
+      <c r="H49" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="50">
@@ -1805,16 +2042,25 @@
         <v>44451</v>
       </c>
       <c r="B50" t="s">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>121</v>
+        <v>59</v>
       </c>
       <c r="D50" t="s">
-        <v>122</v>
-      </c>
-      <c r="E50" t="s">
-        <v>15</v>
+        <v>98</v>
+      </c>
+      <c r="E50" t="n">
+        <v>41</v>
+      </c>
+      <c r="F50" t="n">
+        <v>33</v>
+      </c>
+      <c r="G50" t="s">
+        <v>99</v>
+      </c>
+      <c r="H50" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="51">
@@ -1822,16 +2068,25 @@
         <v>44451</v>
       </c>
       <c r="B51" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="C51" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="D51" t="s">
-        <v>95</v>
-      </c>
-      <c r="E51" t="s">
-        <v>15</v>
+        <v>100</v>
+      </c>
+      <c r="E51" t="n">
+        <v>28</v>
+      </c>
+      <c r="F51" t="n">
+        <v>16</v>
+      </c>
+      <c r="G51" t="s">
+        <v>84</v>
+      </c>
+      <c r="H51" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="52">
@@ -1839,16 +2094,25 @@
         <v>44451</v>
       </c>
       <c r="B52" t="s">
-        <v>125</v>
+        <v>37</v>
       </c>
       <c r="C52" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="D52" t="s">
-        <v>37</v>
-      </c>
-      <c r="E52" t="s">
-        <v>15</v>
+        <v>101</v>
+      </c>
+      <c r="E52" t="n">
+        <v>20</v>
+      </c>
+      <c r="F52" t="n">
+        <v>16</v>
+      </c>
+      <c r="G52" t="s">
+        <v>44</v>
+      </c>
+      <c r="H52" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="53">
@@ -1856,16 +2120,25 @@
         <v>44458</v>
       </c>
       <c r="B53" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="C53" t="s">
-        <v>127</v>
+        <v>48</v>
       </c>
       <c r="D53" t="s">
-        <v>95</v>
-      </c>
-      <c r="E53" t="s">
-        <v>15</v>
+        <v>49</v>
+      </c>
+      <c r="E53" t="n">
+        <v>17</v>
+      </c>
+      <c r="F53" t="n">
+        <v>11</v>
+      </c>
+      <c r="G53" t="s">
+        <v>84</v>
+      </c>
+      <c r="H53" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="54">
@@ -1873,16 +2146,25 @@
         <v>44458</v>
       </c>
       <c r="B54" t="s">
-        <v>128</v>
+        <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="D54" t="s">
-        <v>75</v>
-      </c>
-      <c r="E54" t="s">
-        <v>15</v>
+        <v>102</v>
+      </c>
+      <c r="E54" t="n">
+        <v>26</v>
+      </c>
+      <c r="F54" t="n">
+        <v>17</v>
+      </c>
+      <c r="G54" t="s">
+        <v>71</v>
+      </c>
+      <c r="H54" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="55">
@@ -1890,16 +2172,25 @@
         <v>44486</v>
       </c>
       <c r="B55" t="s">
-        <v>130</v>
+        <v>37</v>
       </c>
       <c r="C55" t="s">
-        <v>131</v>
+        <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>32</v>
-      </c>
-      <c r="E55" t="s">
-        <v>8</v>
+        <v>103</v>
+      </c>
+      <c r="E55" t="n">
+        <v>6</v>
+      </c>
+      <c r="F55" t="n">
+        <v>34</v>
+      </c>
+      <c r="G55" t="s">
+        <v>40</v>
+      </c>
+      <c r="H55" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="56">
@@ -1907,16 +2198,25 @@
         <v>44507</v>
       </c>
       <c r="B56" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>133</v>
+        <v>38</v>
       </c>
       <c r="D56" t="s">
-        <v>95</v>
-      </c>
-      <c r="E56" t="s">
-        <v>8</v>
+        <v>104</v>
+      </c>
+      <c r="E56" t="n">
+        <v>16</v>
+      </c>
+      <c r="F56" t="n">
+        <v>23</v>
+      </c>
+      <c r="G56" t="s">
+        <v>84</v>
+      </c>
+      <c r="H56" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="57">
@@ -1924,16 +2224,25 @@
         <v>44521</v>
       </c>
       <c r="B57" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="C57" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="D57" t="s">
-        <v>135</v>
-      </c>
-      <c r="E57" t="s">
-        <v>15</v>
+        <v>105</v>
+      </c>
+      <c r="E57" t="n">
+        <v>30</v>
+      </c>
+      <c r="F57" t="n">
+        <v>10</v>
+      </c>
+      <c r="G57" t="s">
+        <v>106</v>
+      </c>
+      <c r="H57" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="58">
@@ -1941,16 +2250,25 @@
         <v>44535</v>
       </c>
       <c r="B58" t="s">
-        <v>136</v>
+        <v>37</v>
       </c>
       <c r="C58" t="s">
-        <v>137</v>
+        <v>63</v>
       </c>
       <c r="D58" t="s">
-        <v>37</v>
-      </c>
-      <c r="E58" t="s">
-        <v>15</v>
+        <v>107</v>
+      </c>
+      <c r="E58" t="n">
+        <v>41</v>
+      </c>
+      <c r="F58" t="n">
+        <v>22</v>
+      </c>
+      <c r="G58" t="s">
+        <v>44</v>
+      </c>
+      <c r="H58" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="59">
@@ -1958,16 +2276,25 @@
         <v>44563</v>
       </c>
       <c r="B59" t="s">
-        <v>138</v>
+        <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="D59" t="s">
-        <v>140</v>
-      </c>
-      <c r="E59" t="s">
-        <v>8</v>
+        <v>108</v>
+      </c>
+      <c r="E59" t="n">
+        <v>23</v>
+      </c>
+      <c r="F59" t="n">
+        <v>20</v>
+      </c>
+      <c r="G59" t="s">
+        <v>109</v>
+      </c>
+      <c r="H59" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="60">
@@ -1975,16 +2302,25 @@
         <v>44836</v>
       </c>
       <c r="B60" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="C60" t="s">
-        <v>141</v>
+        <v>59</v>
       </c>
       <c r="D60" t="s">
-        <v>32</v>
-      </c>
-      <c r="E60" t="s">
-        <v>61</v>
+        <v>60</v>
+      </c>
+      <c r="E60" t="n">
+        <v>48</v>
+      </c>
+      <c r="F60" t="n">
+        <v>45</v>
+      </c>
+      <c r="G60" t="s">
+        <v>40</v>
+      </c>
+      <c r="H60" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="61">
@@ -1992,16 +2328,25 @@
         <v>44843</v>
       </c>
       <c r="B61" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="C61" t="s">
-        <v>142</v>
+        <v>57</v>
       </c>
       <c r="D61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E61" t="s">
-        <v>15</v>
+        <v>58</v>
+      </c>
+      <c r="E61" t="n">
+        <v>30</v>
+      </c>
+      <c r="F61" t="n">
+        <v>28</v>
+      </c>
+      <c r="G61" t="s">
+        <v>21</v>
+      </c>
+      <c r="H61" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="62">
@@ -2009,16 +2354,25 @@
         <v>44850</v>
       </c>
       <c r="B62" t="s">
-        <v>143</v>
+        <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>144</v>
+        <v>76</v>
       </c>
       <c r="D62" t="s">
-        <v>87</v>
-      </c>
-      <c r="E62" t="s">
-        <v>8</v>
+        <v>110</v>
+      </c>
+      <c r="E62" t="n">
+        <v>14</v>
+      </c>
+      <c r="F62" t="n">
+        <v>28</v>
+      </c>
+      <c r="G62" t="s">
+        <v>79</v>
+      </c>
+      <c r="H62" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="63">
@@ -2026,16 +2380,25 @@
         <v>44871</v>
       </c>
       <c r="B63" t="s">
-        <v>145</v>
+        <v>37</v>
       </c>
       <c r="C63" t="s">
-        <v>146</v>
+        <v>76</v>
       </c>
       <c r="D63" t="s">
-        <v>147</v>
-      </c>
-      <c r="E63" t="s">
-        <v>15</v>
+        <v>111</v>
+      </c>
+      <c r="E63" t="n">
+        <v>20</v>
+      </c>
+      <c r="F63" t="n">
+        <v>17</v>
+      </c>
+      <c r="G63" t="s">
+        <v>112</v>
+      </c>
+      <c r="H63" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="64">
@@ -2043,16 +2406,25 @@
         <v>44871</v>
       </c>
       <c r="B64" t="s">
-        <v>148</v>
+        <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>149</v>
+        <v>25</v>
       </c>
       <c r="D64" t="s">
-        <v>147</v>
-      </c>
-      <c r="E64" t="s">
-        <v>8</v>
+        <v>113</v>
+      </c>
+      <c r="E64" t="n">
+        <v>20</v>
+      </c>
+      <c r="F64" t="n">
+        <v>27</v>
+      </c>
+      <c r="G64" t="s">
+        <v>112</v>
+      </c>
+      <c r="H64" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="65">
@@ -2060,16 +2432,25 @@
         <v>45179</v>
       </c>
       <c r="B65" t="s">
-        <v>150</v>
+        <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>151</v>
+        <v>67</v>
       </c>
       <c r="D65" t="s">
-        <v>152</v>
-      </c>
-      <c r="E65" t="s">
-        <v>15</v>
+        <v>114</v>
+      </c>
+      <c r="E65" t="n">
+        <v>30</v>
+      </c>
+      <c r="F65" t="n">
+        <v>7</v>
+      </c>
+      <c r="G65" t="s">
+        <v>115</v>
+      </c>
+      <c r="H65" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="66">
@@ -2077,16 +2458,25 @@
         <v>45186</v>
       </c>
       <c r="B66" t="s">
-        <v>153</v>
+        <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>154</v>
+        <v>22</v>
       </c>
       <c r="D66" t="s">
-        <v>18</v>
-      </c>
-      <c r="E66" t="s">
-        <v>8</v>
+        <v>116</v>
+      </c>
+      <c r="E66" t="n">
+        <v>10</v>
+      </c>
+      <c r="F66" t="n">
+        <v>38</v>
+      </c>
+      <c r="G66" t="s">
+        <v>24</v>
+      </c>
+      <c r="H66" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="67">
@@ -2094,16 +2484,25 @@
         <v>45186</v>
       </c>
       <c r="B67" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="C67" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="D67" t="s">
-        <v>115</v>
-      </c>
-      <c r="E67" t="s">
-        <v>15</v>
+        <v>60</v>
+      </c>
+      <c r="E67" t="n">
+        <v>37</v>
+      </c>
+      <c r="F67" t="n">
+        <v>31</v>
+      </c>
+      <c r="G67" t="s">
+        <v>95</v>
+      </c>
+      <c r="H67" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="68">
@@ -2111,16 +2510,25 @@
         <v>45214</v>
       </c>
       <c r="B68" t="s">
-        <v>156</v>
+        <v>18</v>
       </c>
       <c r="C68" t="s">
-        <v>157</v>
+        <v>63</v>
       </c>
       <c r="D68" t="s">
-        <v>32</v>
-      </c>
-      <c r="E68" t="s">
-        <v>8</v>
+        <v>117</v>
+      </c>
+      <c r="E68" t="n">
+        <v>13</v>
+      </c>
+      <c r="F68" t="n">
+        <v>17</v>
+      </c>
+      <c r="G68" t="s">
+        <v>40</v>
+      </c>
+      <c r="H68" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="69">
@@ -2128,16 +2536,25 @@
         <v>45214</v>
       </c>
       <c r="B69" t="s">
-        <v>158</v>
+        <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>159</v>
+        <v>57</v>
       </c>
       <c r="D69" t="s">
-        <v>122</v>
-      </c>
-      <c r="E69" t="s">
-        <v>15</v>
+        <v>118</v>
+      </c>
+      <c r="E69" t="n">
+        <v>17</v>
+      </c>
+      <c r="F69" t="n">
+        <v>19</v>
+      </c>
+      <c r="G69" t="s">
+        <v>99</v>
+      </c>
+      <c r="H69" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="70">
@@ -2145,16 +2562,25 @@
         <v>45235</v>
       </c>
       <c r="B70" t="s">
-        <v>160</v>
+        <v>18</v>
       </c>
       <c r="C70" t="s">
-        <v>161</v>
+        <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>162</v>
-      </c>
-      <c r="E70" t="s">
-        <v>8</v>
+        <v>119</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3</v>
+      </c>
+      <c r="F70" t="n">
+        <v>37</v>
+      </c>
+      <c r="G70" t="s">
+        <v>120</v>
+      </c>
+      <c r="H70" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="71">
@@ -2162,16 +2588,25 @@
         <v>45242</v>
       </c>
       <c r="B71" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>163</v>
+        <v>25</v>
       </c>
       <c r="D71" t="s">
-        <v>95</v>
-      </c>
-      <c r="E71" t="s">
-        <v>15</v>
+        <v>105</v>
+      </c>
+      <c r="E71" t="n">
+        <v>34</v>
+      </c>
+      <c r="F71" t="n">
+        <v>3</v>
+      </c>
+      <c r="G71" t="s">
+        <v>84</v>
+      </c>
+      <c r="H71" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="72">
@@ -2179,16 +2614,25 @@
         <v>45249</v>
       </c>
       <c r="B72" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>165</v>
+        <v>31</v>
       </c>
       <c r="D72" t="s">
-        <v>166</v>
-      </c>
-      <c r="E72" t="s">
-        <v>8</v>
+        <v>121</v>
+      </c>
+      <c r="E72" t="n">
+        <v>13</v>
+      </c>
+      <c r="F72" t="n">
+        <v>20</v>
+      </c>
+      <c r="G72" t="s">
+        <v>122</v>
+      </c>
+      <c r="H72" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="73">
@@ -2196,16 +2640,25 @@
         <v>45263</v>
       </c>
       <c r="B73" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C73" t="s">
-        <v>167</v>
+        <v>45</v>
       </c>
       <c r="D73" t="s">
-        <v>105</v>
-      </c>
-      <c r="E73" t="s">
-        <v>15</v>
+        <v>46</v>
+      </c>
+      <c r="E73" t="n">
+        <v>6</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="s">
+        <v>90</v>
+      </c>
+      <c r="H73" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="74">
@@ -2213,16 +2666,25 @@
         <v>45291</v>
       </c>
       <c r="B74" t="s">
-        <v>138</v>
+        <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>168</v>
+        <v>35</v>
       </c>
       <c r="D74" t="s">
-        <v>11</v>
-      </c>
-      <c r="E74" t="s">
-        <v>8</v>
+        <v>108</v>
+      </c>
+      <c r="E74" t="n">
+        <v>20</v>
+      </c>
+      <c r="F74" t="n">
+        <v>23</v>
+      </c>
+      <c r="G74" t="s">
+        <v>16</v>
+      </c>
+      <c r="H74" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="75">
@@ -2230,16 +2692,25 @@
         <v>45291</v>
       </c>
       <c r="B75" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>169</v>
+        <v>41</v>
       </c>
       <c r="D75" t="s">
-        <v>170</v>
-      </c>
-      <c r="E75" t="s">
-        <v>15</v>
+        <v>42</v>
+      </c>
+      <c r="E75" t="n">
+        <v>27</v>
+      </c>
+      <c r="F75" t="n">
+        <v>10</v>
+      </c>
+      <c r="G75" t="s">
+        <v>123</v>
+      </c>
+      <c r="H75" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="76">
@@ -2247,16 +2718,25 @@
         <v>45550</v>
       </c>
       <c r="B76" t="s">
-        <v>171</v>
+        <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>172</v>
+        <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>173</v>
-      </c>
-      <c r="E76" t="s">
-        <v>8</v>
+        <v>124</v>
+      </c>
+      <c r="E76" t="n">
+        <v>26</v>
+      </c>
+      <c r="F76" t="n">
+        <v>23</v>
+      </c>
+      <c r="G76" t="s">
+        <v>125</v>
+      </c>
+      <c r="H76" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="77">
@@ -2264,16 +2744,25 @@
         <v>45550</v>
       </c>
       <c r="B77" t="s">
-        <v>174</v>
+        <v>37</v>
       </c>
       <c r="C77" t="s">
-        <v>175</v>
+        <v>9</v>
       </c>
       <c r="D77" t="s">
-        <v>176</v>
-      </c>
-      <c r="E77" t="s">
-        <v>15</v>
+        <v>126</v>
+      </c>
+      <c r="E77" t="n">
+        <v>26</v>
+      </c>
+      <c r="F77" t="n">
+        <v>3</v>
+      </c>
+      <c r="G77" t="s">
+        <v>127</v>
+      </c>
+      <c r="H77" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="78">
@@ -2281,16 +2770,25 @@
         <v>45550</v>
       </c>
       <c r="B78" t="s">
-        <v>177</v>
+        <v>18</v>
       </c>
       <c r="C78" t="s">
-        <v>139</v>
+        <v>45</v>
       </c>
       <c r="D78" t="s">
-        <v>87</v>
-      </c>
-      <c r="E78" t="s">
-        <v>15</v>
+        <v>128</v>
+      </c>
+      <c r="E78" t="n">
+        <v>23</v>
+      </c>
+      <c r="F78" t="n">
+        <v>20</v>
+      </c>
+      <c r="G78" t="s">
+        <v>79</v>
+      </c>
+      <c r="H78" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="79">
@@ -2298,16 +2796,25 @@
         <v>45557</v>
       </c>
       <c r="B79" t="s">
-        <v>178</v>
+        <v>37</v>
       </c>
       <c r="C79" t="s">
-        <v>179</v>
+        <v>67</v>
       </c>
       <c r="D79" t="s">
-        <v>32</v>
-      </c>
-      <c r="E79" t="s">
-        <v>8</v>
+        <v>129</v>
+      </c>
+      <c r="E79" t="n">
+        <v>10</v>
+      </c>
+      <c r="F79" t="n">
+        <v>20</v>
+      </c>
+      <c r="G79" t="s">
+        <v>40</v>
+      </c>
+      <c r="H79" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="80">
@@ -2315,16 +2822,25 @@
         <v>45585</v>
       </c>
       <c r="B80" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="C80" t="s">
-        <v>180</v>
+        <v>76</v>
       </c>
       <c r="D80" t="s">
-        <v>32</v>
-      </c>
-      <c r="E80" t="s">
-        <v>15</v>
+        <v>77</v>
+      </c>
+      <c r="E80" t="n">
+        <v>34</v>
+      </c>
+      <c r="F80" t="n">
+        <v>14</v>
+      </c>
+      <c r="G80" t="s">
+        <v>40</v>
+      </c>
+      <c r="H80" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="81">
@@ -2332,16 +2848,25 @@
         <v>45599</v>
       </c>
       <c r="B81" t="s">
-        <v>181</v>
+        <v>13</v>
       </c>
       <c r="C81" t="s">
-        <v>182</v>
+        <v>63</v>
       </c>
       <c r="D81" t="s">
-        <v>183</v>
-      </c>
-      <c r="E81" t="s">
-        <v>8</v>
+        <v>130</v>
+      </c>
+      <c r="E81" t="n">
+        <v>24</v>
+      </c>
+      <c r="F81" t="n">
+        <v>41</v>
+      </c>
+      <c r="G81" t="s">
+        <v>131</v>
+      </c>
+      <c r="H81" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="82">
@@ -2349,16 +2874,25 @@
         <v>45599</v>
       </c>
       <c r="B82" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="C82" t="s">
-        <v>169</v>
+        <v>57</v>
       </c>
       <c r="D82" t="s">
-        <v>184</v>
-      </c>
-      <c r="E82" t="s">
-        <v>15</v>
+        <v>58</v>
+      </c>
+      <c r="E82" t="n">
+        <v>27</v>
+      </c>
+      <c r="F82" t="n">
+        <v>10</v>
+      </c>
+      <c r="G82" t="s">
+        <v>132</v>
+      </c>
+      <c r="H82" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="83">
@@ -2366,16 +2900,25 @@
         <v>45606</v>
       </c>
       <c r="B83" t="s">
+        <v>8</v>
+      </c>
+      <c r="C83" t="s">
+        <v>28</v>
+      </c>
+      <c r="D83" t="s">
         <v>62</v>
       </c>
-      <c r="C83" t="s">
-        <v>139</v>
-      </c>
-      <c r="D83" t="s">
-        <v>135</v>
-      </c>
-      <c r="E83" t="s">
-        <v>15</v>
+      <c r="E83" t="n">
+        <v>23</v>
+      </c>
+      <c r="F83" t="n">
+        <v>20</v>
+      </c>
+      <c r="G83" t="s">
+        <v>106</v>
+      </c>
+      <c r="H83" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="84">
@@ -2383,16 +2926,25 @@
         <v>45613</v>
       </c>
       <c r="B84" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>185</v>
+        <v>31</v>
       </c>
       <c r="D84" t="s">
-        <v>183</v>
-      </c>
-      <c r="E84" t="s">
-        <v>8</v>
+        <v>121</v>
+      </c>
+      <c r="E84" t="n">
+        <v>19</v>
+      </c>
+      <c r="F84" t="n">
+        <v>34</v>
+      </c>
+      <c r="G84" t="s">
+        <v>131</v>
+      </c>
+      <c r="H84" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="85">
@@ -2400,16 +2952,25 @@
         <v>45627</v>
       </c>
       <c r="B85" t="s">
-        <v>145</v>
+        <v>37</v>
       </c>
       <c r="C85" t="s">
-        <v>186</v>
+        <v>76</v>
       </c>
       <c r="D85" t="s">
-        <v>14</v>
-      </c>
-      <c r="E85" t="s">
-        <v>15</v>
+        <v>111</v>
+      </c>
+      <c r="E85" t="n">
+        <v>17</v>
+      </c>
+      <c r="F85" t="n">
+        <v>13</v>
+      </c>
+      <c r="G85" t="s">
+        <v>21</v>
+      </c>
+      <c r="H85" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="86">
@@ -2417,16 +2978,25 @@
         <v>45627</v>
       </c>
       <c r="B86" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C86" t="s">
-        <v>187</v>
+        <v>19</v>
       </c>
       <c r="D86" t="s">
-        <v>24</v>
-      </c>
-      <c r="E86" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="E86" t="n">
+        <v>26</v>
+      </c>
+      <c r="F86" t="n">
+        <v>21</v>
+      </c>
+      <c r="G86" t="s">
+        <v>30</v>
+      </c>
+      <c r="H86" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="87">
@@ -2434,16 +3004,25 @@
         <v>45634</v>
       </c>
       <c r="B87" t="s">
-        <v>188</v>
+        <v>13</v>
       </c>
       <c r="C87" t="s">
-        <v>189</v>
+        <v>28</v>
       </c>
       <c r="D87" t="s">
-        <v>27</v>
-      </c>
-      <c r="E87" t="s">
-        <v>8</v>
+        <v>133</v>
+      </c>
+      <c r="E87" t="n">
+        <v>13</v>
+      </c>
+      <c r="F87" t="n">
+        <v>28</v>
+      </c>
+      <c r="G87" t="s">
+        <v>33</v>
+      </c>
+      <c r="H87" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="88">
@@ -2451,16 +3030,25 @@
         <v>45654</v>
       </c>
       <c r="B88" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C88" t="s">
-        <v>190</v>
+        <v>45</v>
       </c>
       <c r="D88" t="s">
-        <v>91</v>
-      </c>
-      <c r="E88" t="s">
-        <v>15</v>
+        <v>46</v>
+      </c>
+      <c r="E88" t="n">
+        <v>40</v>
+      </c>
+      <c r="F88" t="n">
+        <v>7</v>
+      </c>
+      <c r="G88" t="s">
+        <v>82</v>
+      </c>
+      <c r="H88" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="89">
@@ -2468,16 +3056,25 @@
         <v>45907</v>
       </c>
       <c r="B89" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="D89" t="s">
-        <v>37</v>
-      </c>
-      <c r="E89" t="s">
-        <v>15</v>
+        <v>87</v>
+      </c>
+      <c r="E89" t="n">
+        <v>20</v>
+      </c>
+      <c r="F89" t="n">
+        <v>13</v>
+      </c>
+      <c r="G89" t="s">
+        <v>44</v>
+      </c>
+      <c r="H89" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="90">
@@ -2485,16 +3082,25 @@
         <v>45914</v>
       </c>
       <c r="B90" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="C90" t="s">
-        <v>192</v>
+        <v>67</v>
       </c>
       <c r="D90" t="s">
-        <v>11</v>
-      </c>
-      <c r="E90" t="s">
-        <v>15</v>
+        <v>68</v>
+      </c>
+      <c r="E90" t="n">
+        <v>31</v>
+      </c>
+      <c r="F90" t="n">
+        <v>17</v>
+      </c>
+      <c r="G90" t="s">
+        <v>16</v>
+      </c>
+      <c r="H90" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="91">
@@ -2502,16 +3108,25 @@
         <v>45921</v>
       </c>
       <c r="B91" t="s">
-        <v>193</v>
+        <v>13</v>
       </c>
       <c r="C91" t="s">
-        <v>182</v>
+        <v>41</v>
       </c>
       <c r="D91" t="s">
-        <v>37</v>
-      </c>
-      <c r="E91" t="s">
-        <v>8</v>
+        <v>134</v>
+      </c>
+      <c r="E91" t="n">
+        <v>24</v>
+      </c>
+      <c r="F91" t="n">
+        <v>41</v>
+      </c>
+      <c r="G91" t="s">
+        <v>44</v>
+      </c>
+      <c r="H91" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="92">
@@ -2519,16 +3134,25 @@
         <v>45928</v>
       </c>
       <c r="B92" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C92" t="s">
-        <v>194</v>
+        <v>38</v>
       </c>
       <c r="D92" t="s">
-        <v>91</v>
-      </c>
-      <c r="E92" t="s">
-        <v>15</v>
+        <v>39</v>
+      </c>
+      <c r="E92" t="n">
+        <v>18</v>
+      </c>
+      <c r="F92" t="n">
+        <v>21</v>
+      </c>
+      <c r="G92" t="s">
+        <v>82</v>
+      </c>
+      <c r="H92" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="93">
@@ -2536,16 +3160,25 @@
         <v>45935</v>
       </c>
       <c r="B93" t="s">
-        <v>138</v>
+        <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>195</v>
+        <v>35</v>
       </c>
       <c r="D93" t="s">
-        <v>27</v>
-      </c>
-      <c r="E93" t="s">
-        <v>8</v>
+        <v>108</v>
+      </c>
+      <c r="E93" t="n">
+        <v>6</v>
+      </c>
+      <c r="F93" t="n">
+        <v>40</v>
+      </c>
+      <c r="G93" t="s">
+        <v>33</v>
+      </c>
+      <c r="H93" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="94">
@@ -2553,16 +3186,25 @@
         <v>45942</v>
       </c>
       <c r="B94" t="s">
-        <v>196</v>
+        <v>18</v>
       </c>
       <c r="C94" t="s">
-        <v>197</v>
+        <v>25</v>
       </c>
       <c r="D94" t="s">
-        <v>152</v>
-      </c>
-      <c r="E94" t="s">
-        <v>15</v>
+        <v>135</v>
+      </c>
+      <c r="E94" t="n">
+        <v>20</v>
+      </c>
+      <c r="F94" t="n">
+        <v>12</v>
+      </c>
+      <c r="G94" t="s">
+        <v>115</v>
+      </c>
+      <c r="H94" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="95">
@@ -2570,16 +3212,25 @@
         <v>45942</v>
       </c>
       <c r="B95" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="C95" t="s">
-        <v>198</v>
+        <v>31</v>
       </c>
       <c r="D95" t="s">
-        <v>87</v>
-      </c>
-      <c r="E95" t="s">
-        <v>15</v>
+        <v>72</v>
+      </c>
+      <c r="E95" t="n">
+        <v>29</v>
+      </c>
+      <c r="F95" t="n">
+        <v>27</v>
+      </c>
+      <c r="G95" t="s">
+        <v>79</v>
+      </c>
+      <c r="H95" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="96">
@@ -2587,16 +3238,25 @@
         <v>45963</v>
       </c>
       <c r="B96" t="s">
-        <v>101</v>
+        <v>8</v>
       </c>
       <c r="C96" t="s">
-        <v>199</v>
+        <v>38</v>
       </c>
       <c r="D96" t="s">
-        <v>147</v>
-      </c>
-      <c r="E96" t="s">
-        <v>15</v>
+        <v>88</v>
+      </c>
+      <c r="E96" t="n">
+        <v>34</v>
+      </c>
+      <c r="F96" t="n">
+        <v>24</v>
+      </c>
+      <c r="G96" t="s">
+        <v>112</v>
+      </c>
+      <c r="H96" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="97">
@@ -2604,16 +3264,25 @@
         <v>45977</v>
       </c>
       <c r="B97" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C97" t="s">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="D97" t="s">
-        <v>95</v>
-      </c>
-      <c r="E97" t="s">
-        <v>8</v>
+        <v>51</v>
+      </c>
+      <c r="E97" t="n">
+        <v>6</v>
+      </c>
+      <c r="F97" t="n">
+        <v>35</v>
+      </c>
+      <c r="G97" t="s">
+        <v>84</v>
+      </c>
+      <c r="H97" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="98">
@@ -2621,16 +3290,25 @@
         <v>45991</v>
       </c>
       <c r="B98" t="s">
-        <v>158</v>
+        <v>8</v>
       </c>
       <c r="C98" t="s">
-        <v>201</v>
+        <v>57</v>
       </c>
       <c r="D98" t="s">
-        <v>202</v>
-      </c>
-      <c r="E98" t="s">
-        <v>15</v>
+        <v>118</v>
+      </c>
+      <c r="E98" t="n">
+        <v>26</v>
+      </c>
+      <c r="F98" t="n">
+        <v>8</v>
+      </c>
+      <c r="G98" t="s">
+        <v>136</v>
+      </c>
+      <c r="H98" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="99">
@@ -2638,16 +3316,25 @@
         <v>45998</v>
       </c>
       <c r="B99" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="C99" t="s">
-        <v>203</v>
+        <v>76</v>
       </c>
       <c r="D99" t="s">
-        <v>98</v>
-      </c>
-      <c r="E99" t="s">
-        <v>15</v>
+        <v>77</v>
+      </c>
+      <c r="E99" t="n">
+        <v>37</v>
+      </c>
+      <c r="F99" t="n">
+        <v>9</v>
+      </c>
+      <c r="G99" t="s">
+        <v>86</v>
+      </c>
+      <c r="H99" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="100">
@@ -2655,16 +3342,25 @@
         <v>46005</v>
       </c>
       <c r="B100" t="s">
-        <v>204</v>
+        <v>13</v>
       </c>
       <c r="C100" t="s">
-        <v>205</v>
+        <v>48</v>
       </c>
       <c r="D100" t="s">
-        <v>206</v>
-      </c>
-      <c r="E100" t="s">
-        <v>8</v>
+        <v>137</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>31</v>
+      </c>
+      <c r="G100" t="s">
+        <v>138</v>
+      </c>
+      <c r="H100" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="101">
@@ -2672,16 +3368,25 @@
         <v>46019</v>
       </c>
       <c r="B101" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="C101" t="s">
-        <v>169</v>
+        <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>135</v>
-      </c>
-      <c r="E101" t="s">
-        <v>15</v>
+        <v>61</v>
+      </c>
+      <c r="E101" t="n">
+        <v>27</v>
+      </c>
+      <c r="F101" t="n">
+        <v>10</v>
+      </c>
+      <c r="G101" t="s">
+        <v>106</v>
+      </c>
+      <c r="H101" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/NFL_Odds/Data/WestCoast_ATS_Analysis.xlsx
+++ b/NFL_Odds/Data/WestCoast_ATS_Analysis.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="157">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -89,6 +89,18 @@
     <t xml:space="preserve">+7.5</t>
   </si>
   <si>
+    <t xml:space="preserve">LA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA @ DET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2.5</t>
+  </si>
+  <si>
     <t xml:space="preserve">JAX</t>
   </si>
   <si>
@@ -107,6 +119,9 @@
     <t xml:space="preserve">+1.0</t>
   </si>
   <si>
+    <t xml:space="preserve">LA @ NYJ</t>
+  </si>
+  <si>
     <t xml:space="preserve">MIA</t>
   </si>
   <si>
@@ -119,15 +134,36 @@
     <t xml:space="preserve">Push</t>
   </si>
   <si>
+    <t xml:space="preserve">NE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA @ NE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+13.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD @ CAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD @ CLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.5</t>
+  </si>
+  <si>
     <t xml:space="preserve">IND</t>
   </si>
   <si>
     <t xml:space="preserve">SF @ IND</t>
   </si>
   <si>
-    <t xml:space="preserve">LAC</t>
-  </si>
-  <si>
     <t xml:space="preserve">NYG</t>
   </si>
   <si>
@@ -146,12 +182,6 @@
     <t xml:space="preserve">OAK @ BUF</t>
   </si>
   <si>
-    <t xml:space="preserve">+2.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NE</t>
-  </si>
-  <si>
     <t xml:space="preserve">LAC @ NE</t>
   </si>
   <si>
@@ -164,7 +194,10 @@
     <t xml:space="preserve">SF @ PHI</t>
   </si>
   <si>
-    <t xml:space="preserve">+13.0</t>
+    <t xml:space="preserve">LA @ NYG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.5</t>
   </si>
   <si>
     <t xml:space="preserve">LAC @ JAX</t>
@@ -185,15 +218,9 @@
     <t xml:space="preserve">OAK @ MIA</t>
   </si>
   <si>
-    <t xml:space="preserve">CLE</t>
-  </si>
-  <si>
     <t xml:space="preserve">LAC @ CLE</t>
   </si>
   <si>
-    <t xml:space="preserve">DET</t>
-  </si>
-  <si>
     <t xml:space="preserve">SEA @ DET</t>
   </si>
   <si>
@@ -203,12 +230,21 @@
     <t xml:space="preserve">SF @ TB</t>
   </si>
   <si>
+    <t xml:space="preserve">-10.5</t>
+  </si>
+  <si>
     <t xml:space="preserve">CIN</t>
   </si>
   <si>
     <t xml:space="preserve">OAK @ CIN</t>
   </si>
   <si>
+    <t xml:space="preserve">LA @ CAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.5</t>
+  </si>
+  <si>
     <t xml:space="preserve">SF @ CIN</t>
   </si>
   <si>
@@ -239,12 +275,18 @@
     <t xml:space="preserve">SEA @ CLE</t>
   </si>
   <si>
+    <t xml:space="preserve">ATL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA @ ATL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">-10.0</t>
   </si>
   <si>
-    <t xml:space="preserve">ATL</t>
-  </si>
-  <si>
     <t xml:space="preserve">SEA @ ATL</t>
   </si>
   <si>
@@ -266,15 +308,21 @@
     <t xml:space="preserve">LV @ CAR</t>
   </si>
   <si>
-    <t xml:space="preserve">-3.0</t>
-  </si>
-  <si>
     <t xml:space="preserve">SF @ NYJ</t>
   </si>
   <si>
     <t xml:space="preserve">-7.0</t>
   </si>
   <si>
+    <t xml:space="preserve">LA @ PHI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA @ BUF</t>
+  </si>
+  <si>
     <t xml:space="preserve">LV @ NE</t>
   </si>
   <si>
@@ -284,15 +332,18 @@
     <t xml:space="preserve">SEA @ MIA</t>
   </si>
   <si>
-    <t xml:space="preserve">-4.5</t>
-  </si>
-  <si>
     <t xml:space="preserve">LAC @ TB</t>
   </si>
   <si>
+    <t xml:space="preserve">LA @ WAS</t>
+  </si>
+  <si>
     <t xml:space="preserve">LV @ CLE</t>
   </si>
   <si>
+    <t xml:space="preserve">LA @ MIA</t>
+  </si>
+  <si>
     <t xml:space="preserve">SEA @ BUF</t>
   </si>
   <si>
@@ -320,6 +371,12 @@
     <t xml:space="preserve">LAC @ WAS</t>
   </si>
   <si>
+    <t xml:space="preserve">LA @ IND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">LV @ PIT</t>
   </si>
   <si>
@@ -338,6 +395,9 @@
     <t xml:space="preserve">LAC @ CIN</t>
   </si>
   <si>
+    <t xml:space="preserve">LA @ BAL</t>
+  </si>
+  <si>
     <t xml:space="preserve">LV @ IND</t>
   </si>
   <si>
@@ -359,9 +419,6 @@
     <t xml:space="preserve">SF @ PIT</t>
   </si>
   <si>
-    <t xml:space="preserve">-1.5</t>
-  </si>
-  <si>
     <t xml:space="preserve">LV @ BUF</t>
   </si>
   <si>
@@ -420,9 +477,6 @@
   </si>
   <si>
     <t xml:space="preserve">SEA @ JAX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.5</t>
   </si>
   <si>
     <t xml:space="preserve">LV @ PHI</t>
@@ -895,51 +949,51 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>42666</v>
+        <v>42659</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>42673</v>
+        <v>42666</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F7" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
@@ -947,129 +1001,129 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>42701</v>
+        <v>42673</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" t="n">
+        <v>30</v>
+      </c>
+      <c r="F8" t="n">
         <v>24</v>
       </c>
-      <c r="F8" t="n">
-        <v>31</v>
-      </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H8" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>43016</v>
+        <v>42687</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
         <v>35</v>
       </c>
-      <c r="D9" t="s">
-        <v>36</v>
-      </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="G9" t="s">
         <v>21</v>
       </c>
       <c r="H9" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>43016</v>
+        <v>42701</v>
       </c>
       <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F10" t="n">
+        <v>31</v>
+      </c>
+      <c r="G10" t="s">
         <v>38</v>
       </c>
-      <c r="D10" t="s">
+      <c r="H10" t="s">
         <v>39</v>
-      </c>
-      <c r="E10" t="n">
-        <v>27</v>
-      </c>
-      <c r="F10" t="n">
-        <v>22</v>
-      </c>
-      <c r="G10" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>43023</v>
+        <v>42708</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
         <v>41</v>
       </c>
-      <c r="D11" t="s">
-        <v>42</v>
-      </c>
       <c r="E11" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
         <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>43037</v>
+        <v>42715</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F12" t="n">
+        <v>28</v>
+      </c>
+      <c r="G12" t="s">
         <v>34</v>
-      </c>
-      <c r="G12" t="s">
-        <v>44</v>
       </c>
       <c r="H12" t="s">
         <v>12</v>
@@ -1077,10 +1131,10 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>43037</v>
+        <v>42728</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
         <v>45</v>
@@ -1089,10 +1143,10 @@
         <v>46</v>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G13" t="s">
         <v>47</v>
@@ -1103,7 +1157,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>43037</v>
+        <v>43016</v>
       </c>
       <c r="B14" t="s">
         <v>8</v>
@@ -1115,13 +1169,13 @@
         <v>49</v>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F14" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G14" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="H14" t="s">
         <v>12</v>
@@ -1129,22 +1183,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>43051</v>
+        <v>43016</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
         <v>51</v>
       </c>
       <c r="E15" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G15" t="s">
         <v>52</v>
@@ -1155,36 +1209,36 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>43093</v>
+        <v>43023</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E16" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="G16" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="H16" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>43359</v>
+        <v>43037</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
@@ -1193,39 +1247,39 @@
         <v>55</v>
       </c>
       <c r="E17" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F17" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="G17" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="H17" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>43366</v>
+        <v>43037</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D18" t="s">
         <v>56</v>
       </c>
       <c r="E18" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F18" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G18" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="H18" t="s">
         <v>12</v>
@@ -1233,51 +1287,51 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>43387</v>
+        <v>43037</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E19" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G19" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="H19" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>43401</v>
+        <v>43044</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D20" t="s">
         <v>60</v>
       </c>
       <c r="E20" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G20" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="H20" t="s">
         <v>17</v>
@@ -1285,103 +1339,103 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>43429</v>
+        <v>43051</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="E21" t="n">
         <v>17</v>
       </c>
       <c r="F21" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="G21" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="H21" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>43429</v>
+        <v>43093</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D22" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E22" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F22" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="G22" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>43429</v>
+        <v>43359</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="F23" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G23" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="H23" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>43450</v>
+        <v>43366</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D24" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E24" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F24" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G24" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H24" t="s">
         <v>12</v>
@@ -1389,25 +1443,25 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>43723</v>
+        <v>43387</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D25" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E25" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F25" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
@@ -1415,77 +1469,77 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>43723</v>
+        <v>43401</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="D26" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E26" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="H26" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>43723</v>
+        <v>43429</v>
       </c>
       <c r="B27" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="E27" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F27" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G27" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="H27" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>43737</v>
+        <v>43429</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D28" t="s">
         <v>70</v>
       </c>
       <c r="E28" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F28" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G28" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="H28" t="s">
         <v>17</v>
@@ -1493,51 +1547,51 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>43737</v>
+        <v>43429</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" t="s">
+        <v>71</v>
+      </c>
+      <c r="E29" t="n">
+        <v>9</v>
+      </c>
+      <c r="F29" t="n">
+        <v>27</v>
+      </c>
+      <c r="G29" t="s">
         <v>31</v>
       </c>
-      <c r="D29" t="s">
-        <v>72</v>
-      </c>
-      <c r="E29" t="n">
-        <v>30</v>
-      </c>
-      <c r="F29" t="n">
-        <v>10</v>
-      </c>
-      <c r="G29" t="s">
-        <v>73</v>
-      </c>
       <c r="H29" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>43751</v>
+        <v>43436</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="E30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F30" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G30" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="H30" t="s">
         <v>17</v>
@@ -1545,25 +1599,25 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>43758</v>
+        <v>43450</v>
       </c>
       <c r="B31" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="E31" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="H31" t="s">
         <v>12</v>
@@ -1571,103 +1625,103 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>43765</v>
+        <v>43716</v>
       </c>
       <c r="B32" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" t="s">
+        <v>75</v>
+      </c>
+      <c r="E32" t="n">
+        <v>30</v>
+      </c>
+      <c r="F32" t="n">
+        <v>27</v>
+      </c>
+      <c r="G32" t="s">
         <v>76</v>
       </c>
-      <c r="D32" t="s">
-        <v>77</v>
-      </c>
-      <c r="E32" t="n">
-        <v>27</v>
-      </c>
-      <c r="F32" t="n">
-        <v>20</v>
-      </c>
-      <c r="G32" t="s">
-        <v>54</v>
-      </c>
       <c r="H32" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>43793</v>
+        <v>43723</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="D33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="F33" t="n">
+        <v>17</v>
+      </c>
+      <c r="G33" t="s">
         <v>34</v>
       </c>
-      <c r="G33" t="s">
-        <v>79</v>
-      </c>
       <c r="H33" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>43793</v>
+        <v>43723</v>
       </c>
       <c r="B34" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D34" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E34" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F34" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G34" t="s">
         <v>21</v>
       </c>
       <c r="H34" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>43800</v>
+        <v>43723</v>
       </c>
       <c r="B35" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
+        <v>80</v>
+      </c>
+      <c r="E35" t="n">
+        <v>28</v>
+      </c>
+      <c r="F35" t="n">
+        <v>26</v>
+      </c>
+      <c r="G35" t="s">
         <v>81</v>
-      </c>
-      <c r="E35" t="n">
-        <v>17</v>
-      </c>
-      <c r="F35" t="n">
-        <v>20</v>
-      </c>
-      <c r="G35" t="s">
-        <v>71</v>
       </c>
       <c r="H35" t="s">
         <v>17</v>
@@ -1675,51 +1729,51 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>43814</v>
+        <v>43737</v>
       </c>
       <c r="B36" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="D36" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="E36" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F36" t="n">
         <v>24</v>
       </c>
       <c r="G36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H36" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>44087</v>
+        <v>43737</v>
       </c>
       <c r="B37" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C37" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E37" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G37" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="H37" t="s">
         <v>17</v>
@@ -1727,25 +1781,25 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>44087</v>
+        <v>43751</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="D38" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E38" t="n">
+        <v>32</v>
+      </c>
+      <c r="F38" t="n">
+        <v>28</v>
+      </c>
+      <c r="G38" t="s">
         <v>34</v>
-      </c>
-      <c r="F38" t="n">
-        <v>30</v>
-      </c>
-      <c r="G38" t="s">
-        <v>84</v>
       </c>
       <c r="H38" t="s">
         <v>17</v>
@@ -1753,25 +1807,25 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>44094</v>
+        <v>43758</v>
       </c>
       <c r="B39" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C39" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="D39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E39" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F39" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G39" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s">
         <v>17</v>
@@ -1779,25 +1833,25 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>44101</v>
+        <v>43758</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C40" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D40" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="E40" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F40" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="H40" t="s">
         <v>12</v>
@@ -1805,77 +1859,77 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>44101</v>
+        <v>43765</v>
       </c>
       <c r="B41" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C41" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="D41" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E41" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F41" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G41" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="H41" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>44108</v>
+        <v>43793</v>
       </c>
       <c r="B42" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D42" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E42" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="G42" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>44108</v>
+        <v>43793</v>
       </c>
       <c r="B43" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="D43" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E43" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F43" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H43" t="s">
         <v>17</v>
@@ -1883,25 +1937,25 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>44136</v>
+        <v>43800</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E44" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G44" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="H44" t="s">
         <v>17</v>
@@ -1909,155 +1963,155 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>44143</v>
+        <v>43814</v>
       </c>
       <c r="B45" t="s">
         <v>18</v>
       </c>
       <c r="C45" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D45" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="E45" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F45" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="G45" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="H45" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>44164</v>
+        <v>44087</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D46" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="F46" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="G46" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="H46" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>44164</v>
+        <v>44087</v>
       </c>
       <c r="B47" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D47" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="E47" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F47" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G47" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>44171</v>
+        <v>44094</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C48" t="s">
         <v>19</v>
       </c>
       <c r="D48" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E48" t="n">
         <v>31</v>
       </c>
       <c r="F48" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G48" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="H48" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>44185</v>
+        <v>44094</v>
       </c>
       <c r="B49" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C49" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="D49" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E49" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F49" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G49" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="H49" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>44451</v>
+        <v>44101</v>
       </c>
       <c r="B50" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C50" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="D50" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E50" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F50" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G50" t="s">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="H50" t="s">
         <v>12</v>
@@ -2065,51 +2119,51 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>44451</v>
+        <v>44101</v>
       </c>
       <c r="B51" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D51" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E51" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F51" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="G51" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="H51" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>44451</v>
+        <v>44101</v>
       </c>
       <c r="B52" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C52" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D52" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E52" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F52" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G52" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s">
         <v>17</v>
@@ -2117,25 +2171,25 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>44458</v>
+        <v>44108</v>
       </c>
       <c r="B53" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C53" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D53" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="E53" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F53" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G53" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="H53" t="s">
         <v>17</v>
@@ -2143,25 +2197,25 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>44458</v>
+        <v>44108</v>
       </c>
       <c r="B54" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C54" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="D54" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E54" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F54" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="G54" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="H54" t="s">
         <v>17</v>
@@ -2169,207 +2223,207 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>44486</v>
+        <v>44115</v>
       </c>
       <c r="B55" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C55" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="D55" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E55" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="F55" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="G55" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="H55" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>44507</v>
+        <v>44136</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D56" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E56" t="n">
         <v>16</v>
       </c>
       <c r="F56" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="G56" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="H56" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>44521</v>
+        <v>44136</v>
       </c>
       <c r="B57" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C57" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D57" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E57" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F57" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="G57" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="H57" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>44535</v>
+        <v>44143</v>
       </c>
       <c r="B58" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="C58" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="D58" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E58" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F58" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="G58" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="H58" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>44563</v>
+        <v>44164</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="D59" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E59" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F59" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="G59" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>44836</v>
+        <v>44164</v>
       </c>
       <c r="B60" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C60" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="D60" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E60" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F60" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="G60" t="s">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="H60" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>44843</v>
+        <v>44171</v>
       </c>
       <c r="B61" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="D61" t="s">
-        <v>58</v>
+        <v>113</v>
       </c>
       <c r="E61" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F61" t="n">
         <v>28</v>
       </c>
       <c r="G61" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="H61" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>44850</v>
+        <v>44185</v>
       </c>
       <c r="B62" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C62" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="D62" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E62" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F62" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="H62" t="s">
         <v>12</v>
@@ -2377,77 +2431,77 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>44871</v>
+        <v>44451</v>
       </c>
       <c r="B63" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="D63" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E63" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="F63" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G63" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H63" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>44871</v>
+        <v>44451</v>
       </c>
       <c r="B64" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="D64" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E64" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F64" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G64" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45179</v>
+        <v>44451</v>
       </c>
       <c r="B65" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="C65" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="D65" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E65" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F65" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G65" t="s">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="H65" t="s">
         <v>17</v>
@@ -2455,25 +2509,25 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45186</v>
+        <v>44458</v>
       </c>
       <c r="B66" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C66" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="D66" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E66" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F66" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G66" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="H66" t="s">
         <v>12</v>
@@ -2481,25 +2535,25 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45186</v>
+        <v>44458</v>
       </c>
       <c r="B67" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C67" t="s">
+        <v>58</v>
+      </c>
+      <c r="D67" t="s">
         <v>59</v>
       </c>
-      <c r="D67" t="s">
-        <v>60</v>
-      </c>
       <c r="E67" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F67" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G67" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H67" t="s">
         <v>17</v>
@@ -2507,51 +2561,51 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>45214</v>
+        <v>44458</v>
       </c>
       <c r="B68" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D68" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E68" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F68" t="n">
         <v>17</v>
       </c>
       <c r="G68" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="H68" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>45214</v>
+        <v>44486</v>
       </c>
       <c r="B69" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="C69" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E69" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F69" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="G69" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="H69" t="s">
         <v>12</v>
@@ -2559,77 +2613,77 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>45235</v>
+        <v>44486</v>
       </c>
       <c r="B70" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D70" t="s">
-        <v>119</v>
+        <v>60</v>
       </c>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="F70" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="G70" t="s">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="H70" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>45242</v>
+        <v>44507</v>
       </c>
       <c r="B71" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D71" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="E71" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="G71" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H71" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>45249</v>
+        <v>44521</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C72" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D72" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E72" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G72" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H72" t="s">
         <v>17</v>
@@ -2637,25 +2691,25 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>45263</v>
+        <v>44535</v>
       </c>
       <c r="B73" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C73" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D73" t="s">
-        <v>46</v>
+        <v>126</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G73" t="s">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="H73" t="s">
         <v>17</v>
@@ -2663,51 +2717,51 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>45291</v>
+        <v>44563</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C74" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="E74" t="n">
         <v>20</v>
       </c>
       <c r="F74" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G74" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="H74" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>45291</v>
+        <v>44563</v>
       </c>
       <c r="B75" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D75" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="E75" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G75" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H75" t="s">
         <v>17</v>
@@ -2715,25 +2769,25 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>45550</v>
+        <v>44836</v>
       </c>
       <c r="B76" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C76" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D76" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="E76" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="F76" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="G76" t="s">
-        <v>125</v>
+        <v>52</v>
       </c>
       <c r="H76" t="s">
         <v>17</v>
@@ -2741,25 +2795,25 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>45550</v>
+        <v>44843</v>
       </c>
       <c r="B77" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C77" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="D77" t="s">
-        <v>126</v>
+        <v>68</v>
       </c>
       <c r="E77" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F77" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="G77" t="s">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="H77" t="s">
         <v>17</v>
@@ -2767,25 +2821,25 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>45550</v>
+        <v>44850</v>
       </c>
       <c r="B78" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="D78" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E78" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F78" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G78" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="H78" t="s">
         <v>12</v>
@@ -2793,233 +2847,233 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>45557</v>
+        <v>44871</v>
       </c>
       <c r="B79" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C79" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="D79" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F79" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G79" t="s">
-        <v>40</v>
+        <v>132</v>
       </c>
       <c r="H79" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>45585</v>
+        <v>44871</v>
       </c>
       <c r="B80" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="D80" t="s">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E80" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F80" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G80" t="s">
-        <v>40</v>
+        <v>132</v>
       </c>
       <c r="H80" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>45599</v>
+        <v>45179</v>
       </c>
       <c r="B81" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D81" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E81" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F81" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G81" t="s">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="H81" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>45599</v>
+        <v>45186</v>
       </c>
       <c r="B82" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C82" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="D82" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="E82" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="G82" t="s">
-        <v>132</v>
+        <v>24</v>
       </c>
       <c r="H82" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>45606</v>
+        <v>45186</v>
       </c>
       <c r="B83" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C83" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D83" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E83" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F83" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G83" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="H83" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>45613</v>
+        <v>45200</v>
       </c>
       <c r="B84" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C84" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D84" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E84" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F84" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G84" t="s">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="H84" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>45627</v>
+        <v>45214</v>
       </c>
       <c r="B85" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="C85" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D85" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="E85" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F85" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G85" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="H85" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>45627</v>
+        <v>45214</v>
       </c>
       <c r="B86" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C86" t="s">
+        <v>45</v>
+      </c>
+      <c r="D86" t="s">
+        <v>137</v>
+      </c>
+      <c r="E86" t="n">
+        <v>17</v>
+      </c>
+      <c r="F86" t="n">
         <v>19</v>
       </c>
-      <c r="D86" t="s">
-        <v>20</v>
-      </c>
-      <c r="E86" t="n">
-        <v>26</v>
-      </c>
-      <c r="F86" t="n">
-        <v>21</v>
-      </c>
       <c r="G86" t="s">
-        <v>30</v>
+        <v>116</v>
       </c>
       <c r="H86" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>45634</v>
+        <v>45235</v>
       </c>
       <c r="B87" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C87" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E87" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F87" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G87" t="s">
-        <v>33</v>
+        <v>139</v>
       </c>
       <c r="H87" t="s">
         <v>12</v>
@@ -3027,25 +3081,25 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>45654</v>
+        <v>45242</v>
       </c>
       <c r="B88" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C88" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D88" t="s">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="E88" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F88" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G88" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H88" t="s">
         <v>17</v>
@@ -3053,25 +3107,25 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>45907</v>
+        <v>45249</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D89" t="s">
-        <v>87</v>
+        <v>140</v>
       </c>
       <c r="E89" t="n">
+        <v>13</v>
+      </c>
+      <c r="F89" t="n">
         <v>20</v>
       </c>
-      <c r="F89" t="n">
-        <v>13</v>
-      </c>
       <c r="G89" t="s">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="H89" t="s">
         <v>17</v>
@@ -3079,25 +3133,25 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>45914</v>
+        <v>45263</v>
       </c>
       <c r="B90" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C90" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="D90" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E90" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="F90" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="H90" t="s">
         <v>17</v>
@@ -3105,77 +3159,77 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>45921</v>
+        <v>45270</v>
       </c>
       <c r="B91" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C91" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E91" t="n">
+        <v>31</v>
+      </c>
+      <c r="F91" t="n">
+        <v>37</v>
+      </c>
+      <c r="G91" t="s">
         <v>24</v>
       </c>
-      <c r="F91" t="n">
-        <v>41</v>
-      </c>
-      <c r="G91" t="s">
-        <v>44</v>
-      </c>
       <c r="H91" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>45928</v>
+        <v>45291</v>
       </c>
       <c r="B92" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C92" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D92" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="E92" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F92" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G92" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="H92" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>45935</v>
+        <v>45291</v>
       </c>
       <c r="B93" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C93" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D93" t="s">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F93" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G93" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="H93" t="s">
         <v>12</v>
@@ -3183,25 +3237,25 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>45942</v>
+        <v>45291</v>
       </c>
       <c r="B94" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C94" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="D94" t="s">
-        <v>135</v>
+        <v>54</v>
       </c>
       <c r="E94" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F94" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G94" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="H94" t="s">
         <v>17</v>
@@ -3209,51 +3263,51 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>45942</v>
+        <v>45550</v>
       </c>
       <c r="B95" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C95" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D95" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="E95" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F95" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G95" t="s">
-        <v>79</v>
+        <v>144</v>
       </c>
       <c r="H95" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>45963</v>
+        <v>45550</v>
       </c>
       <c r="B96" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="C96" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="E96" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F96" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G96" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="H96" t="s">
         <v>17</v>
@@ -3261,25 +3315,25 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>45977</v>
+        <v>45550</v>
       </c>
       <c r="B97" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="C97" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D97" t="s">
-        <v>51</v>
+        <v>147</v>
       </c>
       <c r="E97" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F97" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G97" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="H97" t="s">
         <v>12</v>
@@ -3287,51 +3341,51 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>45991</v>
+        <v>45557</v>
       </c>
       <c r="B98" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="C98" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D98" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="E98" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F98" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G98" t="s">
-        <v>136</v>
+        <v>52</v>
       </c>
       <c r="H98" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>45998</v>
+        <v>45585</v>
       </c>
       <c r="B99" t="s">
         <v>18</v>
       </c>
       <c r="C99" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D99" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="E99" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F99" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G99" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="H99" t="s">
         <v>17</v>
@@ -3339,25 +3393,25 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46005</v>
+        <v>45599</v>
       </c>
       <c r="B100" t="s">
         <v>13</v>
       </c>
       <c r="C100" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="D100" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F100" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G100" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="H100" t="s">
         <v>12</v>
@@ -3365,16 +3419,16 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46019</v>
+        <v>45599</v>
       </c>
       <c r="B101" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C101" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="D101" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E101" t="n">
         <v>27</v>
@@ -3383,9 +3437,633 @@
         <v>10</v>
       </c>
       <c r="G101" t="s">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="H101" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>45606</v>
+      </c>
+      <c r="B102" t="s">
+        <v>8</v>
+      </c>
+      <c r="C102" t="s">
+        <v>32</v>
+      </c>
+      <c r="D102" t="s">
+        <v>71</v>
+      </c>
+      <c r="E102" t="n">
+        <v>23</v>
+      </c>
+      <c r="F102" t="n">
+        <v>20</v>
+      </c>
+      <c r="G102" t="s">
+        <v>125</v>
+      </c>
+      <c r="H102" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>45613</v>
+      </c>
+      <c r="B103" t="s">
+        <v>13</v>
+      </c>
+      <c r="C103" t="s">
+        <v>36</v>
+      </c>
+      <c r="D103" t="s">
+        <v>140</v>
+      </c>
+      <c r="E103" t="n">
+        <v>19</v>
+      </c>
+      <c r="F103" t="n">
+        <v>34</v>
+      </c>
+      <c r="G103" t="s">
+        <v>150</v>
+      </c>
+      <c r="H103" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>45613</v>
+      </c>
+      <c r="B104" t="s">
+        <v>25</v>
+      </c>
+      <c r="C104" t="s">
+        <v>40</v>
+      </c>
+      <c r="D104" t="s">
+        <v>41</v>
+      </c>
+      <c r="E104" t="n">
+        <v>28</v>
+      </c>
+      <c r="F104" t="n">
+        <v>22</v>
+      </c>
+      <c r="G104" t="s">
+        <v>120</v>
+      </c>
+      <c r="H104" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B105" t="s">
+        <v>43</v>
+      </c>
+      <c r="C105" t="s">
+        <v>87</v>
+      </c>
+      <c r="D105" t="s">
+        <v>131</v>
+      </c>
+      <c r="E105" t="n">
+        <v>17</v>
+      </c>
+      <c r="F105" t="n">
+        <v>13</v>
+      </c>
+      <c r="G105" t="s">
+        <v>21</v>
+      </c>
+      <c r="H105" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B106" t="s">
+        <v>18</v>
+      </c>
+      <c r="C106" t="s">
+        <v>19</v>
+      </c>
+      <c r="D106" t="s">
+        <v>20</v>
+      </c>
+      <c r="E106" t="n">
+        <v>26</v>
+      </c>
+      <c r="F106" t="n">
+        <v>21</v>
+      </c>
+      <c r="G106" t="s">
+        <v>34</v>
+      </c>
+      <c r="H106" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>45634</v>
+      </c>
+      <c r="B107" t="s">
+        <v>13</v>
+      </c>
+      <c r="C107" t="s">
+        <v>32</v>
+      </c>
+      <c r="D107" t="s">
+        <v>152</v>
+      </c>
+      <c r="E107" t="n">
+        <v>13</v>
+      </c>
+      <c r="F107" t="n">
+        <v>28</v>
+      </c>
+      <c r="G107" t="s">
+        <v>38</v>
+      </c>
+      <c r="H107" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>45648</v>
+      </c>
+      <c r="B108" t="s">
+        <v>25</v>
+      </c>
+      <c r="C108" t="s">
+        <v>19</v>
+      </c>
+      <c r="D108" t="s">
+        <v>35</v>
+      </c>
+      <c r="E108" t="n">
+        <v>19</v>
+      </c>
+      <c r="F108" t="n">
+        <v>9</v>
+      </c>
+      <c r="G108" t="s">
+        <v>89</v>
+      </c>
+      <c r="H108" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>45654</v>
+      </c>
+      <c r="B109" t="s">
+        <v>43</v>
+      </c>
+      <c r="C109" t="s">
+        <v>40</v>
+      </c>
+      <c r="D109" t="s">
+        <v>56</v>
+      </c>
+      <c r="E109" t="n">
+        <v>40</v>
+      </c>
+      <c r="F109" t="n">
+        <v>7</v>
+      </c>
+      <c r="G109" t="s">
+        <v>96</v>
+      </c>
+      <c r="H109" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>45907</v>
+      </c>
+      <c r="B110" t="s">
+        <v>13</v>
+      </c>
+      <c r="C110" t="s">
+        <v>40</v>
+      </c>
+      <c r="D110" t="s">
+        <v>103</v>
+      </c>
+      <c r="E110" t="n">
+        <v>20</v>
+      </c>
+      <c r="F110" t="n">
+        <v>13</v>
+      </c>
+      <c r="G110" t="s">
+        <v>28</v>
+      </c>
+      <c r="H110" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>45914</v>
+      </c>
+      <c r="B111" t="s">
+        <v>18</v>
+      </c>
+      <c r="C111" t="s">
+        <v>79</v>
+      </c>
+      <c r="D111" t="s">
+        <v>80</v>
+      </c>
+      <c r="E111" t="n">
+        <v>31</v>
+      </c>
+      <c r="F111" t="n">
+        <v>17</v>
+      </c>
+      <c r="G111" t="s">
+        <v>16</v>
+      </c>
+      <c r="H111" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>45921</v>
+      </c>
+      <c r="B112" t="s">
+        <v>25</v>
+      </c>
+      <c r="C112" t="s">
+        <v>58</v>
+      </c>
+      <c r="D112" t="s">
+        <v>100</v>
+      </c>
+      <c r="E112" t="n">
+        <v>26</v>
+      </c>
+      <c r="F112" t="n">
+        <v>33</v>
+      </c>
+      <c r="G112" t="s">
+        <v>16</v>
+      </c>
+      <c r="H112" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>45921</v>
+      </c>
+      <c r="B113" t="s">
+        <v>13</v>
+      </c>
+      <c r="C113" t="s">
+        <v>53</v>
+      </c>
+      <c r="D113" t="s">
+        <v>153</v>
+      </c>
+      <c r="E113" t="n">
+        <v>24</v>
+      </c>
+      <c r="F113" t="n">
+        <v>41</v>
+      </c>
+      <c r="G113" t="s">
+        <v>28</v>
+      </c>
+      <c r="H113" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>45928</v>
+      </c>
+      <c r="B114" t="s">
+        <v>43</v>
+      </c>
+      <c r="C114" t="s">
+        <v>50</v>
+      </c>
+      <c r="D114" t="s">
+        <v>51</v>
+      </c>
+      <c r="E114" t="n">
+        <v>18</v>
+      </c>
+      <c r="F114" t="n">
+        <v>21</v>
+      </c>
+      <c r="G114" t="s">
+        <v>96</v>
+      </c>
+      <c r="H114" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>45935</v>
+      </c>
+      <c r="B115" t="s">
+        <v>13</v>
+      </c>
+      <c r="C115" t="s">
+        <v>48</v>
+      </c>
+      <c r="D115" t="s">
+        <v>128</v>
+      </c>
+      <c r="E115" t="n">
+        <v>6</v>
+      </c>
+      <c r="F115" t="n">
+        <v>40</v>
+      </c>
+      <c r="G115" t="s">
+        <v>38</v>
+      </c>
+      <c r="H115" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>45942</v>
+      </c>
+      <c r="B116" t="s">
+        <v>25</v>
+      </c>
+      <c r="C116" t="s">
+        <v>14</v>
+      </c>
+      <c r="D116" t="s">
+        <v>127</v>
+      </c>
+      <c r="E116" t="n">
+        <v>17</v>
+      </c>
+      <c r="F116" t="n">
+        <v>3</v>
+      </c>
+      <c r="G116" t="s">
+        <v>99</v>
+      </c>
+      <c r="H116" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>45942</v>
+      </c>
+      <c r="B117" t="s">
+        <v>18</v>
+      </c>
+      <c r="C117" t="s">
+        <v>29</v>
+      </c>
+      <c r="D117" t="s">
+        <v>154</v>
+      </c>
+      <c r="E117" t="n">
+        <v>20</v>
+      </c>
+      <c r="F117" t="n">
+        <v>12</v>
+      </c>
+      <c r="G117" t="s">
+        <v>76</v>
+      </c>
+      <c r="H117" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>45942</v>
+      </c>
+      <c r="B118" t="s">
+        <v>43</v>
+      </c>
+      <c r="C118" t="s">
+        <v>36</v>
+      </c>
+      <c r="D118" t="s">
+        <v>84</v>
+      </c>
+      <c r="E118" t="n">
+        <v>29</v>
+      </c>
+      <c r="F118" t="n">
+        <v>27</v>
+      </c>
+      <c r="G118" t="s">
+        <v>93</v>
+      </c>
+      <c r="H118" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>45963</v>
+      </c>
+      <c r="B119" t="s">
+        <v>8</v>
+      </c>
+      <c r="C119" t="s">
+        <v>50</v>
+      </c>
+      <c r="D119" t="s">
+        <v>104</v>
+      </c>
+      <c r="E119" t="n">
+        <v>34</v>
+      </c>
+      <c r="F119" t="n">
+        <v>24</v>
+      </c>
+      <c r="G119" t="s">
+        <v>132</v>
+      </c>
+      <c r="H119" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>45977</v>
+      </c>
+      <c r="B120" t="s">
+        <v>43</v>
+      </c>
+      <c r="C120" t="s">
+        <v>29</v>
+      </c>
+      <c r="D120" t="s">
+        <v>62</v>
+      </c>
+      <c r="E120" t="n">
+        <v>6</v>
+      </c>
+      <c r="F120" t="n">
+        <v>35</v>
+      </c>
+      <c r="G120" t="s">
+        <v>89</v>
+      </c>
+      <c r="H120" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B121" t="s">
+        <v>25</v>
+      </c>
+      <c r="C121" t="s">
+        <v>9</v>
+      </c>
+      <c r="D121" t="s">
+        <v>75</v>
+      </c>
+      <c r="E121" t="n">
+        <v>28</v>
+      </c>
+      <c r="F121" t="n">
+        <v>31</v>
+      </c>
+      <c r="G121" t="s">
+        <v>90</v>
+      </c>
+      <c r="H121" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B122" t="s">
+        <v>8</v>
+      </c>
+      <c r="C122" t="s">
+        <v>45</v>
+      </c>
+      <c r="D122" t="s">
+        <v>137</v>
+      </c>
+      <c r="E122" t="n">
+        <v>26</v>
+      </c>
+      <c r="F122" t="n">
+        <v>8</v>
+      </c>
+      <c r="G122" t="s">
+        <v>61</v>
+      </c>
+      <c r="H122" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>45998</v>
+      </c>
+      <c r="B123" t="s">
+        <v>18</v>
+      </c>
+      <c r="C123" t="s">
+        <v>87</v>
+      </c>
+      <c r="D123" t="s">
+        <v>91</v>
+      </c>
+      <c r="E123" t="n">
+        <v>37</v>
+      </c>
+      <c r="F123" t="n">
+        <v>9</v>
+      </c>
+      <c r="G123" t="s">
+        <v>99</v>
+      </c>
+      <c r="H123" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>46005</v>
+      </c>
+      <c r="B124" t="s">
+        <v>13</v>
+      </c>
+      <c r="C124" t="s">
+        <v>58</v>
+      </c>
+      <c r="D124" t="s">
+        <v>155</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>31</v>
+      </c>
+      <c r="G124" t="s">
+        <v>156</v>
+      </c>
+      <c r="H124" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>46019</v>
+      </c>
+      <c r="B125" t="s">
+        <v>18</v>
+      </c>
+      <c r="C125" t="s">
+        <v>9</v>
+      </c>
+      <c r="D125" t="s">
+        <v>70</v>
+      </c>
+      <c r="E125" t="n">
+        <v>27</v>
+      </c>
+      <c r="F125" t="n">
+        <v>10</v>
+      </c>
+      <c r="G125" t="s">
+        <v>125</v>
+      </c>
+      <c r="H125" t="s">
         <v>17</v>
       </c>
     </row>
